--- a/agent/data/stores/demo_store/store.xlsx
+++ b/agent/data/stores/demo_store/store.xlsx
@@ -9,11 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="הוראות" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מפת החנות" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מוצרים" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מחלקות" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="חריגים" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'מוצרים'!$A$1:$F$97</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -21,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,8 +59,12 @@
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -116,6 +119,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002F5597"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -262,7 +270,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -328,6 +336,20 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -701,121 +723,133 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="40" t="inlineStr">
         <is>
           <t>איך ממלאים את קובץ החנות</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>לשונית 'מפת החנות': מציירים את החנות במבט מלמעלה. כל משבצת היא בערך מטר על מטר.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>לשונית 'מפת החנות': מציירים את החנות במבט מלמעלה. כל משבצת היא בערך מטר על מטר.</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    • משבצת ריקה = מקום שאפשר ללכת בו.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    • משבצת ריקה = מקום שאפשר ללכת בו.</t>
+          <t xml:space="preserve">    • X = מדף, קיר, מקרר או דלפק. מקום שאי אפשר לעבור דרכו.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    • X = מדף, קיר, מקרר או דלפק. מקום שאי אפשר לעבור דרכו.</t>
+          <t xml:space="preserve">    • טקסט (למשל 'מעבר 3', 'חלב וביצים') = המקום שבו הלקוח עומד כשהוא לוקח מוצרים מהאזור.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    • טקסט (למשל 'מעבר 3', 'חלב וביצים') = המקום שבו הלקוח עומד כשהוא לוקח מוצרים מהאזור.</t>
+          <t xml:space="preserve">       אפשר לכתוב בתא אחד, או למזג כמה תאים (Merge) ולכתוב בהם פעם אחת.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">       אפשר לכתוב בתא אחד, או למזג כמה תאים (Merge) ולכתוב בהם פעם אחת.</t>
+          <t xml:space="preserve">    • חובה: תא אחד עם המילה 'כניסה' ותא אחד עם המילה 'קופות'.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">    • חובה: תא אחד עם המילה 'כניסה' ותא אחד עם המילה 'קופות'.</t>
+          <t xml:space="preserve">    • מומלץ להקיף את כל החנות בקיר של X.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    • מומלץ להקיף את כל החנות בקיר של X.</t>
+          <t xml:space="preserve">    • שורה 1 היא להגדרות (שם החנות, כמה מטר כל משבצת). את הציור מתחילים משורה 3.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    • שורה 1 היא להגדרות (שם החנות, כמה מטר כל משבצת). את הציור מתחילים משורה 3.</t>
+          <t xml:space="preserve">    • צבעים לא חובה. הם רק עוזרים לראות את הציור.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    • צבעים לא חובה. הם רק עוזרים לראות את הציור.</t>
+          <t>לשונית 'מחלקות' (חובה): שורה לכל מחלקה.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    • 'אזור' = בדיוק הטקסט שכתבתם בציור (למשל 'מעבר 3'). כמה מחלקות יכולות להיות באותו אזור.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>לשונית 'מוצרים': שורה לכל מוצר.</t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    • 'מה נמכר כאן' = כמה דוגמאות מופרדות בפסיקים. לא צריך רשימה מלאה:</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    • 'אזור' = בדיוק הטקסט שכתבתם בציור (למשל 'מעבר 3').</t>
+          <t xml:space="preserve">       האייג'נט משייך כל מוצר למחלקה המתאימה לפי הדוגמאות ולפי ידע כללי.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">    • 'שמות נוספים' = איך לקוחות עשויים לכתוב את המוצר, מופרדים ב- |</t>
+          <t>לשונית 'חריגים' (לא חובה): רק מוצרים שלא נמצאים במחלקה שהייתם מצפים לה.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    • 'לאסוף בסוף' = 'כן' רק למוצרים שנמסים מהר, כמו גלידה. האזור שלהם יהיה אחרון לפני הקופות.</t>
+          <t xml:space="preserve">    • למשל סוללות ליד הקופות, או חלב סויה במעבר הקפה ולא במקרר החלב.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">    • מק"ט וקטגוריה לא חובה.</t>
+          <t xml:space="preserve">    • 'שמות נוספים' = איך לקוחות עשויים לכתוב את המוצר, מופרדים ב- |</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    • 'לאסוף בסוף' = 'כן' למוצר שנמס מהר. (גלידה וארטיק מזוהים גם בלי זה.)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>אם יש טעות (אזור שלא קיים בציור, אזור חסום, חסרה כניסה) המערכת תציג הודעה שמסבירה מה לתקן.</t>
         </is>
@@ -1056,10 +1090,10 @@
           <t>מאפייה</t>
         </is>
       </c>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="10" t="n"/>
-      <c r="I4" s="10" t="n"/>
-      <c r="J4" s="11" t="n"/>
+      <c r="G4" s="41" t="n"/>
+      <c r="H4" s="41" t="n"/>
+      <c r="I4" s="41" t="n"/>
+      <c r="J4" s="42" t="n"/>
       <c r="K4" s="8" t="n"/>
       <c r="L4" s="8" t="n"/>
       <c r="M4" s="8" t="n"/>
@@ -1069,20 +1103,20 @@
           <t>חלב וביצים</t>
         </is>
       </c>
-      <c r="P4" s="13" t="n"/>
-      <c r="Q4" s="13" t="n"/>
-      <c r="R4" s="13" t="n"/>
-      <c r="S4" s="14" t="n"/>
+      <c r="P4" s="41" t="n"/>
+      <c r="Q4" s="41" t="n"/>
+      <c r="R4" s="41" t="n"/>
+      <c r="S4" s="42" t="n"/>
       <c r="T4" s="8" t="n"/>
       <c r="U4" s="15" t="inlineStr">
         <is>
           <t>בשר ודגים</t>
         </is>
       </c>
-      <c r="V4" s="16" t="n"/>
-      <c r="W4" s="16" t="n"/>
-      <c r="X4" s="16" t="n"/>
-      <c r="Y4" s="17" t="n"/>
+      <c r="V4" s="41" t="n"/>
+      <c r="W4" s="41" t="n"/>
+      <c r="X4" s="41" t="n"/>
+      <c r="Y4" s="42" t="n"/>
       <c r="Z4" s="8" t="n"/>
       <c r="AA4" s="8" t="n"/>
       <c r="AB4" s="8" t="n"/>
@@ -1227,7 +1261,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n"/>
+      <c r="B8" s="43" t="n"/>
       <c r="C8" s="8" t="n"/>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -1350,7 +1384,7 @@
         </is>
       </c>
       <c r="AB8" s="8" t="n"/>
-      <c r="AC8" s="22" t="n"/>
+      <c r="AC8" s="43" t="n"/>
       <c r="AD8" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1363,14 +1397,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="B9" s="20" t="n"/>
+      <c r="B9" s="43" t="n"/>
       <c r="C9" s="8" t="n"/>
       <c r="D9" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E9" s="23" t="n"/>
+      <c r="E9" s="43" t="n"/>
       <c r="F9" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1381,7 +1415,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="H9" s="23" t="n"/>
+      <c r="H9" s="43" t="n"/>
       <c r="I9" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1392,7 +1426,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="K9" s="23" t="n"/>
+      <c r="K9" s="43" t="n"/>
       <c r="L9" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1403,7 +1437,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N9" s="23" t="n"/>
+      <c r="N9" s="43" t="n"/>
       <c r="O9" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1414,7 +1448,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Q9" s="23" t="n"/>
+      <c r="Q9" s="43" t="n"/>
       <c r="R9" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1425,7 +1459,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="T9" s="23" t="n"/>
+      <c r="T9" s="43" t="n"/>
       <c r="U9" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1436,7 +1470,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="W9" s="23" t="n"/>
+      <c r="W9" s="43" t="n"/>
       <c r="X9" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1447,14 +1481,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Z9" s="23" t="n"/>
+      <c r="Z9" s="43" t="n"/>
       <c r="AA9" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="AB9" s="8" t="n"/>
-      <c r="AC9" s="22" t="n"/>
+      <c r="AC9" s="43" t="n"/>
       <c r="AD9" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1467,14 +1501,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n"/>
+      <c r="B10" s="43" t="n"/>
       <c r="C10" s="8" t="n"/>
       <c r="D10" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E10" s="23" t="n"/>
+      <c r="E10" s="43" t="n"/>
       <c r="F10" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1485,7 +1519,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="H10" s="23" t="n"/>
+      <c r="H10" s="43" t="n"/>
       <c r="I10" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1496,7 +1530,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="K10" s="23" t="n"/>
+      <c r="K10" s="43" t="n"/>
       <c r="L10" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1507,7 +1541,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N10" s="23" t="n"/>
+      <c r="N10" s="43" t="n"/>
       <c r="O10" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1518,7 +1552,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Q10" s="23" t="n"/>
+      <c r="Q10" s="43" t="n"/>
       <c r="R10" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1529,7 +1563,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="T10" s="23" t="n"/>
+      <c r="T10" s="43" t="n"/>
       <c r="U10" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1540,7 +1574,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="W10" s="23" t="n"/>
+      <c r="W10" s="43" t="n"/>
       <c r="X10" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1551,14 +1585,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Z10" s="23" t="n"/>
+      <c r="Z10" s="43" t="n"/>
       <c r="AA10" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="AB10" s="8" t="n"/>
-      <c r="AC10" s="22" t="n"/>
+      <c r="AC10" s="43" t="n"/>
       <c r="AD10" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1571,14 +1605,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="B11" s="20" t="n"/>
+      <c r="B11" s="43" t="n"/>
       <c r="C11" s="8" t="n"/>
       <c r="D11" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E11" s="23" t="n"/>
+      <c r="E11" s="43" t="n"/>
       <c r="F11" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1589,7 +1623,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="H11" s="23" t="n"/>
+      <c r="H11" s="43" t="n"/>
       <c r="I11" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1600,7 +1634,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="K11" s="23" t="n"/>
+      <c r="K11" s="43" t="n"/>
       <c r="L11" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1611,7 +1645,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N11" s="23" t="n"/>
+      <c r="N11" s="43" t="n"/>
       <c r="O11" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1622,7 +1656,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Q11" s="23" t="n"/>
+      <c r="Q11" s="43" t="n"/>
       <c r="R11" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1633,7 +1667,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="T11" s="23" t="n"/>
+      <c r="T11" s="43" t="n"/>
       <c r="U11" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1644,7 +1678,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="W11" s="23" t="n"/>
+      <c r="W11" s="43" t="n"/>
       <c r="X11" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1655,14 +1689,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Z11" s="23" t="n"/>
+      <c r="Z11" s="43" t="n"/>
       <c r="AA11" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="AB11" s="8" t="n"/>
-      <c r="AC11" s="22" t="n"/>
+      <c r="AC11" s="43" t="n"/>
       <c r="AD11" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1675,14 +1709,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n"/>
+      <c r="B12" s="43" t="n"/>
       <c r="C12" s="8" t="n"/>
       <c r="D12" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E12" s="23" t="n"/>
+      <c r="E12" s="43" t="n"/>
       <c r="F12" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1693,7 +1727,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="H12" s="23" t="n"/>
+      <c r="H12" s="43" t="n"/>
       <c r="I12" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1704,7 +1738,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="K12" s="23" t="n"/>
+      <c r="K12" s="43" t="n"/>
       <c r="L12" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1715,7 +1749,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N12" s="23" t="n"/>
+      <c r="N12" s="43" t="n"/>
       <c r="O12" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1726,7 +1760,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Q12" s="23" t="n"/>
+      <c r="Q12" s="43" t="n"/>
       <c r="R12" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1737,7 +1771,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="T12" s="23" t="n"/>
+      <c r="T12" s="43" t="n"/>
       <c r="U12" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1748,7 +1782,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="W12" s="23" t="n"/>
+      <c r="W12" s="43" t="n"/>
       <c r="X12" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1759,14 +1793,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Z12" s="23" t="n"/>
+      <c r="Z12" s="43" t="n"/>
       <c r="AA12" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="AB12" s="8" t="n"/>
-      <c r="AC12" s="22" t="n"/>
+      <c r="AC12" s="43" t="n"/>
       <c r="AD12" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1779,14 +1813,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="B13" s="20" t="n"/>
+      <c r="B13" s="43" t="n"/>
       <c r="C13" s="8" t="n"/>
       <c r="D13" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E13" s="23" t="n"/>
+      <c r="E13" s="43" t="n"/>
       <c r="F13" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1797,7 +1831,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="H13" s="23" t="n"/>
+      <c r="H13" s="43" t="n"/>
       <c r="I13" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1808,7 +1842,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="K13" s="23" t="n"/>
+      <c r="K13" s="43" t="n"/>
       <c r="L13" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1819,7 +1853,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N13" s="23" t="n"/>
+      <c r="N13" s="43" t="n"/>
       <c r="O13" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1830,7 +1864,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Q13" s="23" t="n"/>
+      <c r="Q13" s="43" t="n"/>
       <c r="R13" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1841,7 +1875,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="T13" s="23" t="n"/>
+      <c r="T13" s="43" t="n"/>
       <c r="U13" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1852,7 +1886,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="W13" s="23" t="n"/>
+      <c r="W13" s="43" t="n"/>
       <c r="X13" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1863,14 +1897,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Z13" s="23" t="n"/>
+      <c r="Z13" s="43" t="n"/>
       <c r="AA13" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="AB13" s="8" t="n"/>
-      <c r="AC13" s="22" t="n"/>
+      <c r="AC13" s="43" t="n"/>
       <c r="AD13" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1883,14 +1917,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="B14" s="20" t="n"/>
+      <c r="B14" s="43" t="n"/>
       <c r="C14" s="8" t="n"/>
       <c r="D14" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E14" s="23" t="n"/>
+      <c r="E14" s="43" t="n"/>
       <c r="F14" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1901,7 +1935,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="H14" s="23" t="n"/>
+      <c r="H14" s="43" t="n"/>
       <c r="I14" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1912,7 +1946,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="K14" s="23" t="n"/>
+      <c r="K14" s="43" t="n"/>
       <c r="L14" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1923,7 +1957,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N14" s="23" t="n"/>
+      <c r="N14" s="43" t="n"/>
       <c r="O14" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1934,7 +1968,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Q14" s="23" t="n"/>
+      <c r="Q14" s="43" t="n"/>
       <c r="R14" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1945,7 +1979,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="T14" s="23" t="n"/>
+      <c r="T14" s="43" t="n"/>
       <c r="U14" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1956,7 +1990,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="W14" s="23" t="n"/>
+      <c r="W14" s="43" t="n"/>
       <c r="X14" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1967,14 +2001,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Z14" s="23" t="n"/>
+      <c r="Z14" s="43" t="n"/>
       <c r="AA14" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="AB14" s="8" t="n"/>
-      <c r="AC14" s="22" t="n"/>
+      <c r="AC14" s="43" t="n"/>
       <c r="AD14" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1987,14 +2021,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="B15" s="20" t="n"/>
+      <c r="B15" s="43" t="n"/>
       <c r="C15" s="8" t="n"/>
       <c r="D15" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E15" s="23" t="n"/>
+      <c r="E15" s="43" t="n"/>
       <c r="F15" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2005,7 +2039,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="H15" s="23" t="n"/>
+      <c r="H15" s="43" t="n"/>
       <c r="I15" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2016,7 +2050,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="K15" s="23" t="n"/>
+      <c r="K15" s="43" t="n"/>
       <c r="L15" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2027,7 +2061,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N15" s="23" t="n"/>
+      <c r="N15" s="43" t="n"/>
       <c r="O15" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2038,7 +2072,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Q15" s="23" t="n"/>
+      <c r="Q15" s="43" t="n"/>
       <c r="R15" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2049,7 +2083,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="T15" s="23" t="n"/>
+      <c r="T15" s="43" t="n"/>
       <c r="U15" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2060,7 +2094,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="W15" s="23" t="n"/>
+      <c r="W15" s="43" t="n"/>
       <c r="X15" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2071,14 +2105,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Z15" s="23" t="n"/>
+      <c r="Z15" s="43" t="n"/>
       <c r="AA15" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="AB15" s="8" t="n"/>
-      <c r="AC15" s="22" t="n"/>
+      <c r="AC15" s="43" t="n"/>
       <c r="AD15" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2091,14 +2125,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="B16" s="20" t="n"/>
+      <c r="B16" s="43" t="n"/>
       <c r="C16" s="8" t="n"/>
       <c r="D16" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E16" s="23" t="n"/>
+      <c r="E16" s="43" t="n"/>
       <c r="F16" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2109,7 +2143,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="H16" s="23" t="n"/>
+      <c r="H16" s="43" t="n"/>
       <c r="I16" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2120,7 +2154,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="K16" s="23" t="n"/>
+      <c r="K16" s="43" t="n"/>
       <c r="L16" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2131,7 +2165,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N16" s="23" t="n"/>
+      <c r="N16" s="43" t="n"/>
       <c r="O16" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2142,7 +2176,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Q16" s="23" t="n"/>
+      <c r="Q16" s="43" t="n"/>
       <c r="R16" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2153,7 +2187,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="T16" s="23" t="n"/>
+      <c r="T16" s="43" t="n"/>
       <c r="U16" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2164,7 +2198,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="W16" s="23" t="n"/>
+      <c r="W16" s="43" t="n"/>
       <c r="X16" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2175,14 +2209,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Z16" s="23" t="n"/>
+      <c r="Z16" s="43" t="n"/>
       <c r="AA16" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="AB16" s="8" t="n"/>
-      <c r="AC16" s="22" t="n"/>
+      <c r="AC16" s="43" t="n"/>
       <c r="AD16" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2195,14 +2229,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="B17" s="20" t="n"/>
+      <c r="B17" s="43" t="n"/>
       <c r="C17" s="8" t="n"/>
       <c r="D17" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E17" s="23" t="n"/>
+      <c r="E17" s="43" t="n"/>
       <c r="F17" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2213,7 +2247,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="H17" s="23" t="n"/>
+      <c r="H17" s="43" t="n"/>
       <c r="I17" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2224,7 +2258,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="K17" s="23" t="n"/>
+      <c r="K17" s="43" t="n"/>
       <c r="L17" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2235,7 +2269,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N17" s="23" t="n"/>
+      <c r="N17" s="43" t="n"/>
       <c r="O17" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2246,7 +2280,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Q17" s="23" t="n"/>
+      <c r="Q17" s="43" t="n"/>
       <c r="R17" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2257,7 +2291,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="T17" s="23" t="n"/>
+      <c r="T17" s="43" t="n"/>
       <c r="U17" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2268,7 +2302,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="W17" s="23" t="n"/>
+      <c r="W17" s="43" t="n"/>
       <c r="X17" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2279,14 +2313,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Z17" s="23" t="n"/>
+      <c r="Z17" s="43" t="n"/>
       <c r="AA17" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="AB17" s="8" t="n"/>
-      <c r="AC17" s="22" t="n"/>
+      <c r="AC17" s="43" t="n"/>
       <c r="AD17" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2299,14 +2333,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="B18" s="20" t="n"/>
+      <c r="B18" s="43" t="n"/>
       <c r="C18" s="8" t="n"/>
       <c r="D18" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E18" s="23" t="n"/>
+      <c r="E18" s="43" t="n"/>
       <c r="F18" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2317,7 +2351,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="H18" s="23" t="n"/>
+      <c r="H18" s="43" t="n"/>
       <c r="I18" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2328,7 +2362,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="K18" s="23" t="n"/>
+      <c r="K18" s="43" t="n"/>
       <c r="L18" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2339,7 +2373,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N18" s="23" t="n"/>
+      <c r="N18" s="43" t="n"/>
       <c r="O18" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2350,7 +2384,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Q18" s="23" t="n"/>
+      <c r="Q18" s="43" t="n"/>
       <c r="R18" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2361,7 +2395,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="T18" s="23" t="n"/>
+      <c r="T18" s="43" t="n"/>
       <c r="U18" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2372,7 +2406,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="W18" s="23" t="n"/>
+      <c r="W18" s="43" t="n"/>
       <c r="X18" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2383,14 +2417,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Z18" s="23" t="n"/>
+      <c r="Z18" s="43" t="n"/>
       <c r="AA18" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="AB18" s="8" t="n"/>
-      <c r="AC18" s="22" t="n"/>
+      <c r="AC18" s="43" t="n"/>
       <c r="AD18" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2403,14 +2437,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="B19" s="20" t="n"/>
+      <c r="B19" s="43" t="n"/>
       <c r="C19" s="8" t="n"/>
       <c r="D19" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E19" s="23" t="n"/>
+      <c r="E19" s="43" t="n"/>
       <c r="F19" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2421,7 +2455,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="H19" s="23" t="n"/>
+      <c r="H19" s="43" t="n"/>
       <c r="I19" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2432,7 +2466,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="K19" s="23" t="n"/>
+      <c r="K19" s="43" t="n"/>
       <c r="L19" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2443,7 +2477,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N19" s="23" t="n"/>
+      <c r="N19" s="43" t="n"/>
       <c r="O19" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2454,7 +2488,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Q19" s="23" t="n"/>
+      <c r="Q19" s="43" t="n"/>
       <c r="R19" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2465,7 +2499,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="T19" s="23" t="n"/>
+      <c r="T19" s="43" t="n"/>
       <c r="U19" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2476,7 +2510,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="W19" s="23" t="n"/>
+      <c r="W19" s="43" t="n"/>
       <c r="X19" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2487,14 +2521,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Z19" s="23" t="n"/>
+      <c r="Z19" s="43" t="n"/>
       <c r="AA19" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="AB19" s="8" t="n"/>
-      <c r="AC19" s="22" t="n"/>
+      <c r="AC19" s="43" t="n"/>
       <c r="AD19" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2507,14 +2541,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="B20" s="20" t="n"/>
+      <c r="B20" s="43" t="n"/>
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E20" s="23" t="n"/>
+      <c r="E20" s="43" t="n"/>
       <c r="F20" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2525,7 +2559,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="H20" s="23" t="n"/>
+      <c r="H20" s="43" t="n"/>
       <c r="I20" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2536,7 +2570,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="K20" s="23" t="n"/>
+      <c r="K20" s="43" t="n"/>
       <c r="L20" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2547,7 +2581,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N20" s="23" t="n"/>
+      <c r="N20" s="43" t="n"/>
       <c r="O20" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2558,7 +2592,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Q20" s="23" t="n"/>
+      <c r="Q20" s="43" t="n"/>
       <c r="R20" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2569,7 +2603,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="T20" s="23" t="n"/>
+      <c r="T20" s="43" t="n"/>
       <c r="U20" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2580,7 +2614,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="W20" s="23" t="n"/>
+      <c r="W20" s="43" t="n"/>
       <c r="X20" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2591,14 +2625,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Z20" s="23" t="n"/>
+      <c r="Z20" s="43" t="n"/>
       <c r="AA20" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="AB20" s="8" t="n"/>
-      <c r="AC20" s="22" t="n"/>
+      <c r="AC20" s="43" t="n"/>
       <c r="AD20" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2611,14 +2645,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="B21" s="20" t="n"/>
+      <c r="B21" s="43" t="n"/>
       <c r="C21" s="8" t="n"/>
       <c r="D21" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E21" s="23" t="n"/>
+      <c r="E21" s="43" t="n"/>
       <c r="F21" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2629,7 +2663,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="H21" s="23" t="n"/>
+      <c r="H21" s="43" t="n"/>
       <c r="I21" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2640,7 +2674,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="K21" s="23" t="n"/>
+      <c r="K21" s="43" t="n"/>
       <c r="L21" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2651,7 +2685,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N21" s="23" t="n"/>
+      <c r="N21" s="43" t="n"/>
       <c r="O21" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2662,7 +2696,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Q21" s="23" t="n"/>
+      <c r="Q21" s="43" t="n"/>
       <c r="R21" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2673,7 +2707,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="T21" s="23" t="n"/>
+      <c r="T21" s="43" t="n"/>
       <c r="U21" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2684,7 +2718,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="W21" s="23" t="n"/>
+      <c r="W21" s="43" t="n"/>
       <c r="X21" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2695,14 +2729,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Z21" s="23" t="n"/>
+      <c r="Z21" s="43" t="n"/>
       <c r="AA21" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="AB21" s="8" t="n"/>
-      <c r="AC21" s="22" t="n"/>
+      <c r="AC21" s="43" t="n"/>
       <c r="AD21" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2715,14 +2749,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="B22" s="20" t="n"/>
+      <c r="B22" s="43" t="n"/>
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E22" s="24" t="n"/>
+      <c r="E22" s="44" t="n"/>
       <c r="F22" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2733,7 +2767,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="H22" s="24" t="n"/>
+      <c r="H22" s="44" t="n"/>
       <c r="I22" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2744,7 +2778,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="K22" s="24" t="n"/>
+      <c r="K22" s="44" t="n"/>
       <c r="L22" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2755,7 +2789,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N22" s="24" t="n"/>
+      <c r="N22" s="44" t="n"/>
       <c r="O22" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2766,7 +2800,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Q22" s="24" t="n"/>
+      <c r="Q22" s="44" t="n"/>
       <c r="R22" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2777,7 +2811,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="T22" s="24" t="n"/>
+      <c r="T22" s="44" t="n"/>
       <c r="U22" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2788,7 +2822,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="W22" s="24" t="n"/>
+      <c r="W22" s="44" t="n"/>
       <c r="X22" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2799,14 +2833,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Z22" s="24" t="n"/>
+      <c r="Z22" s="44" t="n"/>
       <c r="AA22" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="AB22" s="8" t="n"/>
-      <c r="AC22" s="22" t="n"/>
+      <c r="AC22" s="43" t="n"/>
       <c r="AD22" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2819,7 +2853,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="B23" s="20" t="n"/>
+      <c r="B23" s="43" t="n"/>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
@@ -2846,7 +2880,7 @@
       <c r="Z23" s="8" t="n"/>
       <c r="AA23" s="8" t="n"/>
       <c r="AB23" s="8" t="n"/>
-      <c r="AC23" s="22" t="n"/>
+      <c r="AC23" s="43" t="n"/>
       <c r="AD23" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2859,7 +2893,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="B24" s="25" t="n"/>
+      <c r="B24" s="44" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
@@ -2886,7 +2920,7 @@
       <c r="Z24" s="8" t="n"/>
       <c r="AA24" s="8" t="n"/>
       <c r="AB24" s="8" t="n"/>
-      <c r="AC24" s="26" t="n"/>
+      <c r="AC24" s="44" t="n"/>
       <c r="AD24" s="7" t="inlineStr">
         <is>
           <t>X</t>
@@ -2944,8 +2978,8 @@
           <t>כניסה</t>
         </is>
       </c>
-      <c r="C26" s="28" t="n"/>
-      <c r="D26" s="29" t="n"/>
+      <c r="C26" s="45" t="n"/>
+      <c r="D26" s="46" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
@@ -2968,12 +3002,12 @@
           <t>קופות</t>
         </is>
       </c>
-      <c r="W26" s="31" t="n"/>
-      <c r="X26" s="31" t="n"/>
-      <c r="Y26" s="31" t="n"/>
-      <c r="Z26" s="31" t="n"/>
-      <c r="AA26" s="31" t="n"/>
-      <c r="AB26" s="32" t="n"/>
+      <c r="W26" s="45" t="n"/>
+      <c r="X26" s="45" t="n"/>
+      <c r="Y26" s="45" t="n"/>
+      <c r="Z26" s="45" t="n"/>
+      <c r="AA26" s="45" t="n"/>
+      <c r="AB26" s="46" t="n"/>
       <c r="AC26" s="8" t="n"/>
       <c r="AD26" s="7" t="inlineStr">
         <is>
@@ -2987,9 +3021,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="B27" s="33" t="n"/>
-      <c r="C27" s="34" t="n"/>
-      <c r="D27" s="35" t="n"/>
+      <c r="B27" s="47" t="n"/>
+      <c r="C27" s="48" t="n"/>
+      <c r="D27" s="49" t="n"/>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
@@ -3007,13 +3041,13 @@
       <c r="S27" s="8" t="n"/>
       <c r="T27" s="8" t="n"/>
       <c r="U27" s="8" t="n"/>
-      <c r="V27" s="36" t="n"/>
-      <c r="W27" s="37" t="n"/>
-      <c r="X27" s="37" t="n"/>
-      <c r="Y27" s="37" t="n"/>
-      <c r="Z27" s="37" t="n"/>
-      <c r="AA27" s="37" t="n"/>
-      <c r="AB27" s="38" t="n"/>
+      <c r="V27" s="47" t="n"/>
+      <c r="W27" s="48" t="n"/>
+      <c r="X27" s="48" t="n"/>
+      <c r="Y27" s="48" t="n"/>
+      <c r="Z27" s="48" t="n"/>
+      <c r="AA27" s="48" t="n"/>
+      <c r="AB27" s="49" t="n"/>
       <c r="AC27" s="8" t="n"/>
       <c r="AD27" s="7" t="inlineStr">
         <is>
@@ -3188,8 +3222,8 @@
     <mergeCell ref="B7:B24"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="W8:W22"/>
+    <mergeCell ref="AC7:AC24"/>
     <mergeCell ref="F4:J4"/>
-    <mergeCell ref="AC7:AC24"/>
     <mergeCell ref="K8:K22"/>
     <mergeCell ref="T1:Z1"/>
     <mergeCell ref="O4:S4"/>
@@ -3205,44 +3239,301 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="110" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="50" t="inlineStr">
+        <is>
+          <t>מחלקה</t>
+        </is>
+      </c>
+      <c r="B1" s="50" t="inlineStr">
+        <is>
+          <t>אזור</t>
+        </is>
+      </c>
+      <c r="C1" s="50" t="inlineStr">
+        <is>
+          <t>מה נמכר כאן</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ירקות ופירות</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ירקות ופירות</t>
+        </is>
+      </c>
+      <c r="C2" s="51" t="inlineStr">
+        <is>
+          <t>עגבניות, מלפפונים, בצל, תפוחי אדמה, גזר, פלפל, לימון, תפוחים, בננות, שום, כרוב, חסה, פטרוזיליה, אבוקדו, ענבים</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>מאפייה</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>מאפייה</t>
+        </is>
+      </c>
+      <c r="C3" s="51" t="inlineStr">
+        <is>
+          <t>לחם, לחם אחיד, לחם מלא, חלה, פיתות, לחמניות, בגט, עוגות, רוגלך</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>מוצרי חלב וביצים</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>חלב וביצים</t>
+        </is>
+      </c>
+      <c r="C4" s="51" t="inlineStr">
+        <is>
+          <t>חלב, ביצים, גבינה לבנה, גבינה צהובה, קוטג', יוגורט, חמאה, שמנת, מעדנים, לבנה</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>בשר עוף ודגים</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>בשר ודגים</t>
+        </is>
+      </c>
+      <c r="C5" s="51" t="inlineStr">
+        <is>
+          <t>חזה עוף, כרעיים, בשר טחון, סלמון, דגים, נקניקיות, שניצל, סטייק</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>שתייה</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>מעבר 1</t>
+        </is>
+      </c>
+      <c r="C6" s="51" t="inlineStr">
+        <is>
+          <t>מים מינרליים, מים, סודה, מיץ תפוזים, מיץ, קולה, תרכיז פטל, בירה, יין</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>חטיפים ומתוקים</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>מעבר 2</t>
+        </is>
+      </c>
+      <c r="C7" s="51" t="inlineStr">
+        <is>
+          <t>במבה, ביסלי, צ'יפס, שוקולד, עוגיות, וופלים, סוכריות, בייגלה</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>דגנים ופסטה</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>מעבר 3</t>
+        </is>
+      </c>
+      <c r="C8" s="51" t="inlineStr">
+        <is>
+          <t>אורז, ספגטי, פסטה, פנה, פתיתים, עדשים, חומוס יבש, קוסקוס, בורגול, קטניות</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>שימורים רטבים ותבלינים</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>מעבר 4</t>
+        </is>
+      </c>
+      <c r="C9" s="51" t="inlineStr">
+        <is>
+          <t>רסק עגבניות, תירס, טונה, קטשופ, מיונז, מלח, פלפל שחור, פפריקה, זיתים, חמוצים, תבלינים</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>אפייה וממרחים</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>מעבר 5</t>
+        </is>
+      </c>
+      <c r="C10" s="51" t="inlineStr">
+        <is>
+          <t>קמח, סוכר, שמרים, אבקת אפייה, שמן קנולה, שמן זית, טחינה, ממרח שוקולד, ריבה, דבש</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>קפה תה ודגני בוקר</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>מעבר 6</t>
+        </is>
+      </c>
+      <c r="C11" s="51" t="inlineStr">
+        <is>
+          <t>קפה נמס, קפה טורקי, תה, דגני בוקר, קורנפלקס, שיבולת שועל</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ניקיון</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>מעבר 7</t>
+        </is>
+      </c>
+      <c r="C12" s="51" t="inlineStr">
+        <is>
+          <t>נוזל כלים, אבקת כביסה, מרכך כביסה, אקונומיקה, נוזל לניקוי רצפה, שקיות אשפה, ספוגים, מטאטא, סמרטוט, מגב</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>נייר וטואלטיקה</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>מעבר 8</t>
+        </is>
+      </c>
+      <c r="C13" s="51" t="inlineStr">
+        <is>
+          <t>נייר טואלט, מגבות נייר, מפיות, משחת שיניים, שמפו, סבון ידיים, חיתולים, דאודורנט, קרם הגנה</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>קפואים</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>קפואים</t>
+        </is>
+      </c>
+      <c r="C14" s="51" t="inlineStr">
+        <is>
+          <t>ירקות קפואים, שניצל קפוא, בצק עלים, גלידה, פיצה קפואה, בורקס, ארטיק</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="39" t="inlineStr">
+      <c r="A1" s="50" t="inlineStr">
         <is>
           <t>מק"ט</t>
         </is>
       </c>
-      <c r="B1" s="39" t="inlineStr">
+      <c r="B1" s="50" t="inlineStr">
         <is>
           <t>שם המוצר</t>
         </is>
       </c>
-      <c r="C1" s="39" t="inlineStr">
+      <c r="C1" s="50" t="inlineStr">
         <is>
           <t>שמות נוספים</t>
         </is>
       </c>
-      <c r="D1" s="39" t="inlineStr">
+      <c r="D1" s="50" t="inlineStr">
         <is>
           <t>קטגוריה</t>
         </is>
       </c>
-      <c r="E1" s="39" t="inlineStr">
+      <c r="E1" s="50" t="inlineStr">
         <is>
           <t>אזור</t>
         </is>
       </c>
-      <c r="F1" s="39" t="inlineStr">
+      <c r="F1" s="50" t="inlineStr">
         <is>
           <t>לאסוף בסוף</t>
         </is>
@@ -3251,2607 +3542,92 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P001</t>
+          <t>X001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>עגבניות</t>
+          <t>חלב סויה</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>עגבניה|עגבנייה|עגבניות שרי</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ירקות ופירות</t>
+          <t>משקה סויה|חלב שקדים|משקה שיבולת שועל</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ירקות ופירות</t>
+          <t>מעבר 6</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>X002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>מלפפונים</t>
+          <t>חומוס מוכן</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>מלפפון|מלפפונים לסלט</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ירקות ופירות</t>
+          <t>סלט חומוס|ממרח חומוס</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ירקות ופירות</t>
+          <t>מעבר 4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P003</t>
+          <t>X003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>בצל יבש</t>
+          <t>סוללות</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>בצל|בצלים</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ירקות ופירות</t>
+          <t>סוללה|בטריות|בטריה|סוללות AA|סוללות AAA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ירקות ופירות</t>
+          <t>קופות</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>X004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>תפוחי אדמה</t>
+          <t>מסטיק</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>תפוא|תפודים|תפוח אדמה</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ירקות ופירות</t>
+          <t>מסטיקים|מנטות</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ירקות ופירות</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>P005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>גזר</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>גזרים</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ירקות ופירות</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ירקות ופירות</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>P006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>פלפל אדום</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>פלפל|פלפלים</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ירקות ופירות</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ירקות ופירות</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>P007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>לימון</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>לימונים</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ירקות ופירות</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ירקות ופירות</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>P008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>תפוחי עץ</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>תפוח|תפוחים</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>ירקות ופירות</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>ירקות ופירות</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>P009</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>בננות</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>בננה</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>ירקות ופירות</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>ירקות ופירות</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>P010</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>שום</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ראש שום</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>ירקות ופירות</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>ירקות ופירות</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>P011</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>כרוב</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>כרוב לבן|כרוב סגול</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>ירקות ופירות</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>ירקות ופירות</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>P012</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>חסה</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>חסה ערבית|חסה אייסברג</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>ירקות ופירות</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>ירקות ופירות</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>P020</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>לחם אחיד פרוס</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>לחם|לחם אחיד|לחם לבן</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>מאפייה</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>מאפייה</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>P021</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>לחם מלא</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>לחם חיטה מלאה|לחם שיפון</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>מאפייה</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>מאפייה</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>P022</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>חלה</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>חלות|חלה לשבת</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>מאפייה</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>מאפייה</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>P023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>פיתות</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>פיתה</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>מאפייה</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>מאפייה</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>P024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>לחמניות</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>לחמנייה|לחמניה</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>מאפייה</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>מאפייה</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>P030</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>חלב 3%</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>חלב|חלב רגיל|חלב שלם|קרטון חלב</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>מוצרי חלב</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>חלב וביצים</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>P031</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>חלב 1%</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>חלב דל|חלב 1|חלב דל שומן</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>מוצרי חלב</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>חלב וביצים</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>P032</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ביצים L</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>ביצים|ביצה|תבנית ביצים</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>מוצרי חלב</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>חלב וביצים</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>P033</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>גבינה לבנה 5%</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>גבינה לבנה|גבינה רכה</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>מוצרי חלב</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>חלב וביצים</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>P034</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>גבינה צהובה פרוסה</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>גבינה צהובה|צהובה</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>מוצרי חלב</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>חלב וביצים</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>P035</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>קוטג' 5%</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>קוטג|קוטג'</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>מוצרי חלב</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>חלב וביצים</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>P036</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>יוגורט</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>יוגורטים|יוגורט טבעי</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>מוצרי חלב</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>חלב וביצים</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>P037</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>חמאה</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>חמאה מלוחה|חמאה ללא מלח</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>מוצרי חלב</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>חלב וביצים</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>P038</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>שמנת מתוקה</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>שמנת להקצפה|שמנת</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>מוצרי חלב</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>חלב וביצים</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>P039</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>שמנת חמוצה</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>שמנת 15%</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>מוצרי חלב</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>חלב וביצים</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>P040</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>חזה עוף</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>עוף|חזה|שניצל</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>בשר עוף ודגים</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>בשר ודגים</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>P041</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>כרעיים עוף</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>כרעיים|שוקיים</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>בשר עוף ודגים</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>בשר ודגים</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>P042</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>בשר טחון</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>טחון|בשר טחון בקר</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>בשר עוף ודגים</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>בשר ודגים</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>P043</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>פילה סלמון</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>סלמון|דג סלמון</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>בשר עוף ודגים</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>בשר ודגים</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>P044</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>נקניקיות</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>נקניק|נקניקייה</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>בשר עוף ודגים</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>בשר ודגים</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>P050</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>מים מינרליים 1.5 ליטר</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>מים|בקבוק מים|שישיית מים</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>שתייה</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>מעבר 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>P051</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>סודה</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>מים מוגזים|סודה בבקבוק</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>שתייה</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>מעבר 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>P052</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>מיץ תפוזים</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>מיץ|תפוזים מיץ</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>שתייה</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>מעבר 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>P053</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>משקה קולה</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>קולה|שתייה מוגזת</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>שתייה</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>מעבר 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>P054</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>תרכיז פטל</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>פטל|סירופ</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>שתייה</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>מעבר 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>P060</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>במבה</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>חטיף בוטנים</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>חטיפים ומתוקים</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>מעבר 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>P061</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>ביסלי</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>חטיף מלוח</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>חטיפים ומתוקים</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>מעבר 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>P062</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>צ'יפס תפוחי אדמה</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>צ'יפס|צ׳יפס|חטיף צ'יפס</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>חטיפים ומתוקים</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>מעבר 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>P063</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>שוקולד חלב</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>שוקולד|טבלת שוקולד</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>חטיפים ומתוקים</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>מעבר 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>P064</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>עוגיות</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>עוגיות שוקולד צ'יפס|ביסקוויטים</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>חטיפים ומתוקים</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>מעבר 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>P065</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>וופלים</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>ופלים|ופל</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>חטיפים ומתוקים</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>מעבר 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>P070</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>אורז לבן</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>אורז|אורז פרסי</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>דגנים ופסטה</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>מעבר 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>P071</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>פסטה ספגטי</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>ספגטי|פסטה</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>דגנים ופסטה</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>מעבר 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>P072</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>פסטה פנה</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>פנה|מקרוני</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>דגנים ופסטה</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>מעבר 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>P073</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>פתיתים</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>פתיתים אפויים</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>דגנים ופסטה</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>מעבר 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>P074</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>עדשים כתומות</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>עדשים</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>דגנים ופסטה</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>מעבר 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>P075</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>חומוס יבש</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>גרגרי חומוס</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>דגנים ופסטה</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>מעבר 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>P076</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>קוסקוס</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>קוסקוס דק</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>דגנים ופסטה</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>מעבר 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>P080</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>רסק עגבניות</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>רסק|רסק בפחית</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>שימורים ורטבים</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>מעבר 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>P081</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>תירס בשימורים</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>תירס|קופסת תירס</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>שימורים ורטבים</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>מעבר 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>P082</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>טונה בשמן</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>טונה|קופסת טונה</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>שימורים ורטבים</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>מעבר 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>P083</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>חומוס מוכן</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>סלט חומוס|ממרח חומוס</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>שימורים ורטבים</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>מעבר 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>P084</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>קטשופ</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>רוטב עגבניות</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>שימורים ורטבים</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>מעבר 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>P085</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>מיונז</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>מיונית</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>שימורים ורטבים</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>מעבר 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>P086</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>מלח</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>מלח שולחן|מלח דק</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>שימורים ורטבים</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>מעבר 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>P087</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>פלפל שחור</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>פלפל טחון</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>שימורים ורטבים</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>מעבר 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>P088</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>פפריקה</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>פפריקה מתוקה</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>שימורים ורטבים</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>מעבר 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>P089</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>זיתים</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>זיתים ירוקים|זיתים שחורים</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>שימורים ורטבים</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>מעבר 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>P090</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>קמח לבן</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>קמח|קמח רגיל</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>אפייה וממרחים</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>מעבר 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>P091</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>סוכר לבן</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>סוכר</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>אפייה וממרחים</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>מעבר 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>P092</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>שמרים יבשים</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>שמרים</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>אפייה וממרחים</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>מעבר 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>P093</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>אבקת אפייה</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>אבקה לאפייה</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>אפייה וממרחים</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>מעבר 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>P094</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>שמן קנולה</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>שמן|שמן לטיגון</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>אפייה וממרחים</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>מעבר 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>P095</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>שמן זית</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>שמן זית כתית</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>אפייה וממרחים</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>מעבר 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>P096</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>טחינה גולמית</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>טחינה|טחינה גולמית 100%</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>אפייה וממרחים</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>מעבר 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>P097</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>ממרח שוקולד</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>ממרח|שוקולד למריחה</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>אפייה וממרחים</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>מעבר 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>P098</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>ריבה</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>ריבת תות|ריבת משמש</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>אפייה וממרחים</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>מעבר 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>P099</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>דבש</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>דבש דבורים</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>אפייה וממרחים</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>מעבר 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>P100</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>קפה נמס</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>קפה|נס קפה</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>קפה ותה</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>מעבר 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>P101</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>קפה טורקי</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>קפה שחור</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>קפה ותה</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>מעבר 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>P102</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>תה</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>שקיקי תה|תה ירוק</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>קפה ותה</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>מעבר 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>P103</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>דגני בוקר</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>קורנפלקס|דגנים</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>קפה ותה</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>מעבר 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>P104</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>שיבולת שועל</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>קוואקר|שיבולת</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>קפה ותה</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>מעבר 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>P105</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>חלב סויה</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>משקה סויה</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>קפה ותה</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>מעבר 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>P110</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>נוזל כלים</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>סבון כלים|ניקוי כלים</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>ניקיון</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>מעבר 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>P111</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>אבקת כביסה</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>כביסה|ג'ל כביסה|נוזל כביסה</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>ניקיון</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>מעבר 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>P112</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>מרכך כביסה</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>מרכך</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>ניקיון</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>מעבר 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>P113</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>אקונומיקה</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>מלבין</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>ניקיון</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>מעבר 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>P114</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>נוזל לניקוי רצפה</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>ניקוי רצפה|סבון רצפה</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>ניקיון</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>מעבר 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>P115</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>שקיות אשפה</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>שקיות זבל|שקיות</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>ניקיון</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>מעבר 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>P116</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>ספוגים</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>ספוג|ספוג כלים</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>ניקיון</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>מעבר 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>P120</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>נייר טואלט</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>נייר טואלט 32 גלילים|ני״ט</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>מוצרי נייר וטואלטיקה</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>מעבר 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>P121</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>מגבות נייר</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>מגבות|נייר סופג</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>מוצרי נייר וטואלטיקה</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>מעבר 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>P122</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>מפיות</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>מפית</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>מוצרי נייר וטואלטיקה</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>מעבר 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>P123</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>משחת שיניים</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>משחה</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>מוצרי נייר וטואלטיקה</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>מעבר 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>P124</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>שמפו</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>שמפו לשיער</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>מוצרי נייר וטואלטיקה</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>מעבר 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>P125</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>סבון ידיים</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>סבון|סבון נוזלי</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>מוצרי נייר וטואלטיקה</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>מעבר 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>P126</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>חיתולים</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>טיטולים|חיתולים לתינוק</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>מוצרי נייר וטואלטיקה</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>מעבר 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>P130</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>ירקות קפואים</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>מעורב ירקות קפוא|אפונה קפואה</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>קפואים</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>קפואים</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>P131</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>שניצל קפוא</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>שניצלונים|שניצל תירס</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>קפואים</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>קפואים</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>P132</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>בצק עלים</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>בצק|בצק פריך</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>קפואים</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>קפואים</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>P133</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>גלידה</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>גלידת וניל|ארטיק</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>קפואים</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>קפואים</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>כן</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>P134</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>פיצה קפואה</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>פיצה</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>קפואים</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>קפואים</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>P135</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>בורקס קפוא</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>בורקס</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>קפואים</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>קפואים</t>
+          <t>קופות</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F97"/>
-  <dataValidations count="1">
-    <dataValidation sqref="F2:F3000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"כן"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>